--- a/deliverables/05-electrical/CFU-000-EL-HAC-003_Release-Source-Schedule.xlsx
+++ b/deliverables/05-electrical/CFU-000-EL-HAC-003_Release-Source-Schedule.xlsx
@@ -467,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S148"/>
+  <dimension ref="A1:S150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>100.0-146.7</t>
+          <t>100.0-147.7</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>93.5 / 86.8</t>
+          <t>93.5 / 87.8</t>
         </is>
       </c>
       <c r="R21" s="5" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="Q85" s="4" t="inlineStr">
         <is>
-          <t>150.0 / 24.0</t>
+          <t>146.0 / 22.0</t>
         </is>
       </c>
       <c r="R85" s="5" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>100.0-149.7</t>
+          <t>100.0-150.1</t>
         </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>A-107 headers on rack structure</t>
+          <t>A-107-B1 headers on rack structure</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
@@ -9647,27 +9647,27 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>A-106 headers on rack structure</t>
+          <t>A-107-B2 headers on rack structure</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>A-106</t>
+          <t>A-107</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>LPG / stabiliser OH</t>
+          <t>Light naphtha</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
-          <t>79-&gt;45 (air 35-&gt;40)</t>
+          <t>84-&gt;50 (air 35-&gt;45)</t>
         </is>
       </c>
       <c r="I108" s="4" t="inlineStr"/>
@@ -9734,27 +9734,27 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>A-108 headers on rack structure</t>
+          <t>A-106 headers on rack structure</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>A-108</t>
+          <t>A-106</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Heavy naphtha</t>
+          <t>LPG / stabiliser OH</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>152-&gt;45 (air 35-&gt;40)</t>
+          <t>79-&gt;45 (air 35-&gt;40)</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr"/>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="Q109" s="4" t="inlineStr">
         <is>
-          <t>63.0 / 75.0</t>
+          <t>57.0 / 75.0</t>
         </is>
       </c>
       <c r="R109" s="5" t="inlineStr">
@@ -9821,17 +9821,17 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>A-101-B1 headers on rack structure</t>
+          <t>A-108 headers on rack structure</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>A-101</t>
+          <t>A-108</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Atm. overhead vapour / naphtha (H2S)</t>
+          <t>Heavy naphtha</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
-          <t>134-&gt;60 (air 35-&gt;55)</t>
+          <t>152-&gt;45 (air 35-&gt;40)</t>
         </is>
       </c>
       <c r="I110" s="4" t="inlineStr"/>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>IIB</t>
+          <t>IIA</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="Q110" s="4" t="inlineStr">
         <is>
-          <t>75.0 / 75.0</t>
+          <t>63.0 / 75.0</t>
         </is>
       </c>
       <c r="R110" s="5" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>A-101-B2 headers on rack structure</t>
+          <t>A-101-B1 headers on rack structure</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="Q111" s="4" t="inlineStr">
         <is>
-          <t>81.0 / 75.0</t>
+          <t>75.0 / 75.0</t>
         </is>
       </c>
       <c r="R111" s="5" t="inlineStr">
@@ -9995,27 +9995,27 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>A-103 headers on rack structure</t>
+          <t>A-101-B2 headers on rack structure</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>A-103</t>
+          <t>A-101</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Kerosene</t>
+          <t>Atm. overhead vapour / naphtha (H2S)</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
-          <t>76-&gt;45 (air 35-&gt;40)</t>
+          <t>134-&gt;60 (air 35-&gt;55)</t>
         </is>
       </c>
       <c r="I112" s="4" t="inlineStr"/>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>IIA</t>
+          <t>IIB</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="Q112" s="4" t="inlineStr">
         <is>
-          <t>111.0 / 75.0</t>
+          <t>81.0 / 75.0</t>
         </is>
       </c>
       <c r="R112" s="5" t="inlineStr">
@@ -10082,27 +10082,27 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>A-104 headers on rack structure</t>
+          <t>A-101-B3 headers on rack structure</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>A-104</t>
+          <t>A-101</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>Atm. overhead vapour / naphtha (H2S)</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>128-&gt;55 (air 35-&gt;50)</t>
+          <t>134-&gt;60 (air 35-&gt;55)</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr"/>
@@ -10133,7 +10133,7 @@
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>IIA</t>
+          <t>IIB</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="Q113" s="4" t="inlineStr">
         <is>
-          <t>117.0 / 75.0</t>
+          <t>87.0 / 75.0</t>
         </is>
       </c>
       <c r="R113" s="5" t="inlineStr">
@@ -10169,17 +10169,17 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>A-105 headers on rack structure</t>
+          <t>A-103 headers on rack structure</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>A-105</t>
+          <t>A-103</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>Kerosene</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>254-&gt;60 (air 35-&gt;55)</t>
+          <t>76-&gt;45 (air 35-&gt;40)</t>
         </is>
       </c>
       <c r="I114" s="4" t="inlineStr"/>
@@ -10230,7 +10230,7 @@
       </c>
       <c r="Q114" s="4" t="inlineStr">
         <is>
-          <t>123.0 / 75.0</t>
+          <t>111.0 / 75.0</t>
         </is>
       </c>
       <c r="R114" s="5" t="inlineStr">
@@ -10256,17 +10256,17 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>A-201 headers on rack structure</t>
+          <t>A-104 headers on rack structure</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>A-201</t>
+          <t>A-104</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>LVGO</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>95-&gt;55 (air 35-&gt;50)</t>
+          <t>128-&gt;55 (air 35-&gt;50)</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr"/>
@@ -10317,7 +10317,7 @@
       </c>
       <c r="Q115" s="4" t="inlineStr">
         <is>
-          <t>159.0 / 75.0</t>
+          <t>117.0 / 75.0</t>
         </is>
       </c>
       <c r="R115" s="5" t="inlineStr">
@@ -10343,17 +10343,17 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>A-202 headers on rack structure</t>
+          <t>A-105 headers on rack structure</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>A-202</t>
+          <t>A-105</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>HVGO</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>205-&gt;90 (air 35-&gt;85)</t>
+          <t>254-&gt;60 (air 35-&gt;55)</t>
         </is>
       </c>
       <c r="I116" s="4" t="inlineStr"/>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="Q116" s="4" t="inlineStr">
         <is>
-          <t>165.0 / 75.0</t>
+          <t>123.0 / 75.0</t>
         </is>
       </c>
       <c r="R116" s="5" t="inlineStr">
@@ -10425,39 +10425,35 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Control-valve station</t>
+          <t>Header box plugs / flanges</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1031 (C-101)</t>
+          <t>A-201 headers on rack structure</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>C-101</t>
+          <t>A-201</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Crude vapours / atm. distillates</t>
+          <t>LVGO</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>134 / 361</t>
-        </is>
-      </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t>1.19 / 1.47</t>
-        </is>
-      </c>
+          <t>95-&gt;55 (air 35-&gt;50)</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr"/>
       <c r="J117" s="4" t="inlineStr">
         <is>
           <t>Secondary</t>
@@ -10475,12 +10471,12 @@
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>Z2: R 3</t>
+          <t>Z2: offset 3</t>
         </is>
       </c>
       <c r="N117" s="4" t="inlineStr">
         <is>
-          <t>100.0-104.0</t>
+          <t>112.0-120.5</t>
         </is>
       </c>
       <c r="O117" s="4" t="inlineStr">
@@ -10495,19 +10491,15 @@
       </c>
       <c r="Q117" s="4" t="inlineStr">
         <is>
-          <t>95.0 / 92.5</t>
+          <t>159.0 / 75.0</t>
         </is>
       </c>
       <c r="R117" s="5" t="inlineStr">
         <is>
-          <t>RP 505 valve stations (stem packing, flanges), 3 m</t>
-        </is>
-      </c>
-      <c r="S117" s="5" t="inlineStr">
-        <is>
-          <t>Indicative location (P&amp;ID / piping layout not yet issued)</t>
-        </is>
-      </c>
+          <t>RP 505 elevated flanged equipment, 3 m around (no grade extension: covered by rack/pump sources)</t>
+        </is>
+      </c>
+      <c r="S117" s="5" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="n">
@@ -10520,22 +10512,22 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Control-valve station</t>
+          <t>Header box plugs / flanges</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1050 (C-102)</t>
+          <t>A-202 headers on rack structure</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>C-102</t>
+          <t>A-202</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Kerosene</t>
+          <t>HVGO</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -10545,14 +10537,10 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="I118" s="4" t="inlineStr">
-        <is>
-          <t>1.26</t>
-        </is>
-      </c>
+          <t>205-&gt;90 (air 35-&gt;60)</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr"/>
       <c r="J118" s="4" t="inlineStr">
         <is>
           <t>Secondary</t>
@@ -10570,12 +10558,12 @@
       </c>
       <c r="M118" s="4" t="inlineStr">
         <is>
-          <t>Z2: R 3</t>
+          <t>Z2: offset 3</t>
         </is>
       </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>100.0-104.0</t>
+          <t>112.0-120.5</t>
         </is>
       </c>
       <c r="O118" s="4" t="inlineStr">
@@ -10590,19 +10578,15 @@
       </c>
       <c r="Q118" s="4" t="inlineStr">
         <is>
-          <t>106.5 / 95.2</t>
+          <t>165.0 / 75.0</t>
         </is>
       </c>
       <c r="R118" s="5" t="inlineStr">
         <is>
-          <t>RP 505 valve stations (stem packing, flanges), 3 m</t>
-        </is>
-      </c>
-      <c r="S118" s="5" t="inlineStr">
-        <is>
-          <t>Indicative location (P&amp;ID / piping layout not yet issued)</t>
-        </is>
-      </c>
+          <t>RP 505 elevated flanged equipment, 3 m around (no grade extension: covered by rack/pump sources)</t>
+        </is>
+      </c>
+      <c r="S118" s="5" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="n">
@@ -10620,32 +10604,32 @@
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1060 (C-103)</t>
+          <t>Control valves FV-1031 (C-101)</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>C-103</t>
+          <t>C-101</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>Crude vapours / atm. distillates</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>134 / 361</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.19 / 1.47</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -10685,7 +10669,7 @@
       </c>
       <c r="Q119" s="4" t="inlineStr">
         <is>
-          <t>112.5 / 95.0</t>
+          <t>95.0 / 92.5</t>
         </is>
       </c>
       <c r="R119" s="5" t="inlineStr">
@@ -10715,17 +10699,17 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1070 (C-104)</t>
+          <t>Control valves FV-1050 (C-102)</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>C-104</t>
+          <t>C-102</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>Kerosene</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -10735,12 +10719,12 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>343</t>
+          <t>220</t>
         </is>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -10780,7 +10764,7 @@
       </c>
       <c r="Q120" s="4" t="inlineStr">
         <is>
-          <t>118.5 / 95.3</t>
+          <t>106.5 / 95.2</t>
         </is>
       </c>
       <c r="R120" s="5" t="inlineStr">
@@ -10810,32 +10794,32 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1034, FV-1094, LV-1097, PV-1091 (C-105)</t>
+          <t>Control valves FV-1060 (C-103)</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>C-105</t>
+          <t>C-103</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>LPG / naphtha (stabiliser)</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>79 / 203</t>
+          <t>302</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
@@ -10875,7 +10859,7 @@
       </c>
       <c r="Q121" s="4" t="inlineStr">
         <is>
-          <t>64.0 / 97.0</t>
+          <t>112.5 / 95.0</t>
         </is>
       </c>
       <c r="R121" s="5" t="inlineStr">
@@ -10905,32 +10889,32 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1103, PV-1100 (C-106)</t>
+          <t>Control valves FV-1070 (C-104)</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>C-106</t>
+          <t>C-104</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Light / heavy naphtha</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>84 / 152</t>
+          <t>343</t>
         </is>
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="J122" s="4" t="inlineStr">
@@ -10970,7 +10954,7 @@
       </c>
       <c r="Q122" s="4" t="inlineStr">
         <is>
-          <t>52.0 / 96.5</t>
+          <t>118.5 / 95.3</t>
         </is>
       </c>
       <c r="R122" s="5" t="inlineStr">
@@ -11000,32 +10984,32 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Control valves PV-2010 (C-201)</t>
+          <t>Control valves FV-1034, FV-1094, LV-1097, PV-1091 (C-105)</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>C-201</t>
+          <t>C-105</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Vacuum gas oils / residue (sub-atmospheric)</t>
+          <t>LPG / naphtha (stabiliser)</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>70 / 386</t>
+          <t>79 / 203</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>20 / 60 mbar(a)</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
@@ -11065,7 +11049,7 @@
       </c>
       <c r="Q123" s="4" t="inlineStr">
         <is>
-          <t>175.0 / 92.7</t>
+          <t>64.0 / 97.0</t>
         </is>
       </c>
       <c r="R123" s="5" t="inlineStr">
@@ -11095,17 +11079,17 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Control valves LV-1008, PDV-1005, PDV-1006, PV-1009, TV-1004 (D-101)</t>
+          <t>Control valves FV-1103, PV-1100 (C-106)</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>D-101</t>
+          <t>C-106</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Crude + wash water, 136 C, 11.5 barg</t>
+          <t>Light / heavy naphtha</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -11113,8 +11097,16 @@
           <t>B</t>
         </is>
       </c>
-      <c r="H124" s="4" t="inlineStr"/>
-      <c r="I124" s="4" t="inlineStr"/>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>84 / 152</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
           <t>Secondary</t>
@@ -11152,7 +11144,7 @@
       </c>
       <c r="Q124" s="4" t="inlineStr">
         <is>
-          <t>36.0 / 55.9</t>
+          <t>52.0 / 96.5</t>
         </is>
       </c>
       <c r="R124" s="5" t="inlineStr">
@@ -11182,32 +11174,32 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Control valves LV-1035, PV-1032A, PV-1032B (D-102)</t>
+          <t>Control valves PV-2010 (C-201)</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>D-102</t>
+          <t>C-201</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>Unstabilised naphtha, LPG, sour water (H2S)</t>
+          <t>Vacuum gas oils / residue (sub-atmospheric)</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>70 / 386</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>20 / 60 mbar(a)</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
@@ -11237,7 +11229,7 @@
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>IIB</t>
+          <t>IIA</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
@@ -11247,7 +11239,7 @@
       </c>
       <c r="Q125" s="4" t="inlineStr">
         <is>
-          <t>79.0 / 86.3</t>
+          <t>175.0 / 92.7</t>
         </is>
       </c>
       <c r="R125" s="5" t="inlineStr">
@@ -11277,34 +11269,26 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Control valves LV-9002 (D-103)</t>
+          <t>Control valves LV-1008, PDV-1005, PDV-1006, PV-1009, TV-1004 (D-101)</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>D-103</t>
+          <t>D-101</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>Refinery fuel gas (H2 &lt; 30 vol% assumed)</t>
+          <t>Crude + wash water, 136 C, 11.5 barg</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I126" s="4" t="inlineStr">
-        <is>
-          <t>3.5</t>
-        </is>
-      </c>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr"/>
+      <c r="I126" s="4" t="inlineStr"/>
       <c r="J126" s="4" t="inlineStr">
         <is>
           <t>Secondary</t>
@@ -11332,7 +11316,7 @@
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>IIB</t>
+          <t>IIA</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
@@ -11342,7 +11326,7 @@
       </c>
       <c r="Q126" s="4" t="inlineStr">
         <is>
-          <t>150.0 / 26.4</t>
+          <t>36.0 / 55.9</t>
         </is>
       </c>
       <c r="R126" s="5" t="inlineStr">
@@ -11372,22 +11356,22 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Control valves LV-2028, LV-2029 (D-201)</t>
+          <t>Control valves LV-1035, PV-1032A, PV-1032B (D-102)</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>D-201</t>
+          <t>D-102</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>Hotwell: sour water, slop oil, NCG with H2S</t>
+          <t>Unstabilised naphtha, LPG, sour water (H2S)</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -11397,7 +11381,7 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
@@ -11437,7 +11421,7 @@
       </c>
       <c r="Q127" s="4" t="inlineStr">
         <is>
-          <t>196.0 / 103.3</t>
+          <t>79.0 / 86.3</t>
         </is>
       </c>
       <c r="R127" s="5" t="inlineStr">
@@ -11467,30 +11451,34 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Control valves TV-1041 (E-101)</t>
+          <t>Control valves LV-9002 (D-103)</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>E-101</t>
+          <t>D-103</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Hydrocarbon (crude / products)</t>
+          <t>Refinery fuel gas (H2 &lt; 30 vol% assumed)</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>H 153-&gt;83 / C 30-&gt;56</t>
-        </is>
-      </c>
-      <c r="I128" s="4" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
       <c r="J128" s="4" t="inlineStr">
         <is>
           <t>Secondary</t>
@@ -11518,7 +11506,7 @@
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>IIA</t>
+          <t>IIB</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
@@ -11528,7 +11516,7 @@
       </c>
       <c r="Q128" s="4" t="inlineStr">
         <is>
-          <t>19.5 / 103.2</t>
+          <t>146.0 / 24.4</t>
         </is>
       </c>
       <c r="R128" s="5" t="inlineStr">
@@ -11558,30 +11546,34 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Control valves TV-1043 (E-106)</t>
+          <t>Control valves LV-2028, LV-2029 (D-201)</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>E-106</t>
+          <t>D-201</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>Hydrocarbon (crude / products)</t>
+          <t>Hotwell: sour water, slop oil, NCG with H2S</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>H 240-&gt;160 / C 136-&gt;170</t>
-        </is>
-      </c>
-      <c r="I129" s="4" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
           <t>Secondary</t>
@@ -11609,7 +11601,7 @@
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>IIA</t>
+          <t>IIB</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
@@ -11619,7 +11611,7 @@
       </c>
       <c r="Q129" s="4" t="inlineStr">
         <is>
-          <t>12.5 / 86.2</t>
+          <t>196.0 / 103.3</t>
         </is>
       </c>
       <c r="R129" s="5" t="inlineStr">
@@ -11649,12 +11641,12 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Control valves TV-2017 (E-108)</t>
+          <t>Control valves TV-1041 (E-101)</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>E-108</t>
+          <t>E-101</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
@@ -11669,7 +11661,7 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>H 315-&gt;205 / C 184-&gt;234</t>
+          <t>H 153-&gt;83 / C 30-&gt;56</t>
         </is>
       </c>
       <c r="I130" s="4" t="inlineStr"/>
@@ -11710,7 +11702,7 @@
       </c>
       <c r="Q130" s="4" t="inlineStr">
         <is>
-          <t>23.0 / 86.2</t>
+          <t>19.5 / 103.2</t>
         </is>
       </c>
       <c r="R130" s="5" t="inlineStr">
@@ -11740,12 +11732,12 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Control valves TV-1045 (E-113)</t>
+          <t>Control valves TV-1043 (E-106)</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>E-113</t>
+          <t>E-106</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
@@ -11760,7 +11752,7 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>H 261-&gt;224 / C 186-&gt;186</t>
+          <t>H 240-&gt;160 / C 136-&gt;170</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr"/>
@@ -11801,7 +11793,7 @@
       </c>
       <c r="Q131" s="4" t="inlineStr">
         <is>
-          <t>40.5 / 103.8</t>
+          <t>12.5 / 86.2</t>
         </is>
       </c>
       <c r="R131" s="5" t="inlineStr">
@@ -11831,17 +11823,17 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1011, FV-1012, FV-1013, FV-1014, FV-1015, FV-1016, FV-1017, FV-1018 (H-101)</t>
+          <t>Control valves TV-2017 (E-108)</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>H-101</t>
+          <t>E-108</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Heater charge (crude / atm. residue)</t>
+          <t>Hydrocarbon (crude / products)</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -11851,14 +11843,10 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>274 -&gt; 366</t>
-        </is>
-      </c>
-      <c r="I132" s="4" t="inlineStr">
-        <is>
-          <t>2.37 outlet</t>
-        </is>
-      </c>
+          <t>H 315-&gt;205 / C 184-&gt;234</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="4" t="inlineStr">
         <is>
           <t>Secondary</t>
@@ -11896,7 +11884,7 @@
       </c>
       <c r="Q132" s="4" t="inlineStr">
         <is>
-          <t>98.0 / 62.0</t>
+          <t>23.0 / 86.2</t>
         </is>
       </c>
       <c r="R132" s="5" t="inlineStr">
@@ -11926,17 +11914,17 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1083, FV-2001, FV-2002, FV-2003, FV-2004, PV-2031 (H-201)</t>
+          <t>Control valves TV-1045 (E-113)</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>H-201</t>
+          <t>E-113</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>Heater charge (crude / atm. residue)</t>
+          <t>Hydrocarbon (crude / products)</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -11946,14 +11934,10 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>349 -&gt; 398</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="inlineStr">
-        <is>
-          <t>-0.70 outlet</t>
-        </is>
-      </c>
+          <t>H 261-&gt;224 / C 186-&gt;186</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr">
         <is>
           <t>Secondary</t>
@@ -11991,7 +11975,7 @@
       </c>
       <c r="Q133" s="4" t="inlineStr">
         <is>
-          <t>172.0 / 62.0</t>
+          <t>40.5 / 103.8</t>
         </is>
       </c>
       <c r="R133" s="5" t="inlineStr">
@@ -12021,30 +12005,34 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1001 (P-101)</t>
+          <t>Control valves FV-1011, FV-1012, FV-1013, FV-1014, FV-1015, FV-1016, FV-1017, FV-1018 (H-101)</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>P-101</t>
+          <t>H-101</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Crude (with light ends)</t>
+          <t>Heater charge (crude / atm. residue)</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I134" s="4" t="inlineStr"/>
+          <t>274 -&gt; 366</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>2.37 outlet</t>
+        </is>
+      </c>
       <c r="J134" s="4" t="inlineStr">
         <is>
           <t>Secondary</t>
@@ -12082,7 +12070,7 @@
       </c>
       <c r="Q134" s="4" t="inlineStr">
         <is>
-          <t>15.5 / 88.0</t>
+          <t>98.0 / 62.0</t>
         </is>
       </c>
       <c r="R134" s="5" t="inlineStr">
@@ -12112,30 +12100,34 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1034 (P-104)</t>
+          <t>Control valves FV-1083, FV-2001, FV-2002, FV-2003, FV-2004, PV-2031 (H-201)</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>P-104</t>
+          <t>H-201</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>Unstabilised naphtha (C3/C4)</t>
+          <t>Heater charge (crude / atm. residue)</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="inlineStr"/>
+          <t>349 -&gt; 398</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>-0.70 outlet</t>
+        </is>
+      </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
           <t>Secondary</t>
@@ -12173,7 +12165,7 @@
       </c>
       <c r="Q135" s="4" t="inlineStr">
         <is>
-          <t>80.5 / 88.0</t>
+          <t>172.0 / 62.0</t>
         </is>
       </c>
       <c r="R135" s="5" t="inlineStr">
@@ -12203,27 +12195,27 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1040 (P-106)</t>
+          <t>Control valves FV-1001 (P-101)</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>P-106</t>
+          <t>P-101</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>TPA (kerosene range)</t>
+          <t>Crude (with light ends)</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I136" s="4" t="inlineStr"/>
@@ -12264,7 +12256,7 @@
       </c>
       <c r="Q136" s="4" t="inlineStr">
         <is>
-          <t>126.0 / 88.0</t>
+          <t>15.5 / 88.0</t>
         </is>
       </c>
       <c r="R136" s="5" t="inlineStr">
@@ -12294,27 +12286,27 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1042 (P-107)</t>
+          <t>Control valves FV-1034 (P-104)</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>P-107</t>
+          <t>P-104</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>MPA</t>
+          <t>Unstabilised naphtha (C3/C4)</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr"/>
@@ -12355,7 +12347,7 @@
       </c>
       <c r="Q137" s="4" t="inlineStr">
         <is>
-          <t>132.5 / 88.0</t>
+          <t>80.5 / 88.0</t>
         </is>
       </c>
       <c r="R137" s="5" t="inlineStr">
@@ -12385,17 +12377,17 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1044 (P-108)</t>
+          <t>Control valves FV-1040 (P-106)</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>P-108</t>
+          <t>P-106</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>BPA</t>
+          <t>TPA (kerosene range)</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -12405,7 +12397,7 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>153</t>
         </is>
       </c>
       <c r="I138" s="4" t="inlineStr"/>
@@ -12446,7 +12438,7 @@
       </c>
       <c r="Q138" s="4" t="inlineStr">
         <is>
-          <t>100.0 / 88.0</t>
+          <t>126.0 / 88.0</t>
         </is>
       </c>
       <c r="R138" s="5" t="inlineStr">
@@ -12476,17 +12468,17 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1052 (P-109)</t>
+          <t>Control valves FV-1042 (P-107)</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>P-109</t>
+          <t>P-107</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>Kerosene</t>
+          <t>MPA</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
@@ -12496,7 +12488,7 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>240</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr"/>
@@ -12537,7 +12529,7 @@
       </c>
       <c r="Q139" s="4" t="inlineStr">
         <is>
-          <t>106.5 / 88.0</t>
+          <t>132.5 / 88.0</t>
         </is>
       </c>
       <c r="R139" s="5" t="inlineStr">
@@ -12567,17 +12559,17 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1062 (P-110)</t>
+          <t>Control valves FV-1044 (P-108)</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>P-110</t>
+          <t>P-108</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Diesel</t>
+          <t>BPA</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -12587,7 +12579,7 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>314</t>
         </is>
       </c>
       <c r="I140" s="4" t="inlineStr"/>
@@ -12628,7 +12620,7 @@
       </c>
       <c r="Q140" s="4" t="inlineStr">
         <is>
-          <t>113.0 / 88.0</t>
+          <t>100.0 / 88.0</t>
         </is>
       </c>
       <c r="R140" s="5" t="inlineStr">
@@ -12658,17 +12650,17 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1072 (P-111)</t>
+          <t>Control valves FV-1052 (P-109)</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>P-111</t>
+          <t>P-109</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>Kerosene</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
@@ -12678,7 +12670,7 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr"/>
@@ -12719,7 +12711,7 @@
       </c>
       <c r="Q141" s="4" t="inlineStr">
         <is>
-          <t>119.5 / 88.0</t>
+          <t>106.5 / 88.0</t>
         </is>
       </c>
       <c r="R141" s="5" t="inlineStr">
@@ -12749,27 +12741,27 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1093 (P-115)</t>
+          <t>Control valves FV-1062 (P-110)</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>P-115</t>
+          <t>P-110</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>294</t>
         </is>
       </c>
       <c r="I142" s="4" t="inlineStr"/>
@@ -12810,7 +12802,7 @@
       </c>
       <c r="Q142" s="4" t="inlineStr">
         <is>
-          <t>64.5 / 88.0</t>
+          <t>113.0 / 88.0</t>
         </is>
       </c>
       <c r="R142" s="5" t="inlineStr">
@@ -12840,27 +12832,27 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1102 (P-116)</t>
+          <t>Control valves FV-1072 (P-111)</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>P-116</t>
+          <t>P-111</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>Light naphtha</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>335</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr"/>
@@ -12901,7 +12893,7 @@
       </c>
       <c r="Q143" s="4" t="inlineStr">
         <is>
-          <t>51.5 / 88.0</t>
+          <t>119.5 / 88.0</t>
         </is>
       </c>
       <c r="R143" s="5" t="inlineStr">
@@ -12931,27 +12923,27 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-1107 (P-117)</t>
+          <t>Control valves FV-1093 (P-115)</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>P-117</t>
+          <t>P-115</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>Heavy naphtha</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I144" s="4" t="inlineStr"/>
@@ -12992,7 +12984,7 @@
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>58.0 / 88.0</t>
+          <t>64.5 / 88.0</t>
         </is>
       </c>
       <c r="R144" s="5" t="inlineStr">
@@ -13022,27 +13014,27 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-2011, FV-2015 (P-201)</t>
+          <t>Control valves FV-1102 (P-116)</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>P-201</t>
+          <t>P-116</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>LVGO</t>
+          <t>Light naphtha</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr"/>
@@ -13083,7 +13075,7 @@
       </c>
       <c r="Q145" s="4" t="inlineStr">
         <is>
-          <t>193.0 / 88.0</t>
+          <t>51.5 / 88.0</t>
         </is>
       </c>
       <c r="R145" s="5" t="inlineStr">
@@ -13113,27 +13105,27 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-2016, FV-2019 (P-202)</t>
+          <t>Control valves FV-1107 (P-117)</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>P-202</t>
+          <t>P-117</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>HVGO</t>
+          <t>Heavy naphtha</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>152</t>
         </is>
       </c>
       <c r="I146" s="4" t="inlineStr"/>
@@ -13174,7 +13166,7 @@
       </c>
       <c r="Q146" s="4" t="inlineStr">
         <is>
-          <t>186.5 / 88.0</t>
+          <t>58.0 / 88.0</t>
         </is>
       </c>
       <c r="R146" s="5" t="inlineStr">
@@ -13204,17 +13196,17 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-2022 (P-203)</t>
+          <t>Control valves FV-2011, FV-2015 (P-201)</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>P-203</t>
+          <t>P-201</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>Slop wax</t>
+          <t>LVGO</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -13224,7 +13216,7 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>224</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr"/>
@@ -13265,7 +13257,7 @@
       </c>
       <c r="Q147" s="4" t="inlineStr">
         <is>
-          <t>180.0 / 88.0</t>
+          <t>193.0 / 88.0</t>
         </is>
       </c>
       <c r="R147" s="5" t="inlineStr">
@@ -13295,17 +13287,17 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Control valves FV-2025 (P-204)</t>
+          <t>Control valves FV-2016, FV-2019 (P-202)</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>P-204</t>
+          <t>P-202</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>Vacuum residue &gt; AIT</t>
+          <t>HVGO</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -13315,7 +13307,7 @@
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>315</t>
         </is>
       </c>
       <c r="I148" s="4" t="inlineStr"/>
@@ -13356,15 +13348,197 @@
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
+          <t>186.5 / 88.0</t>
+        </is>
+      </c>
+      <c r="R148" s="5" t="inlineStr">
+        <is>
+          <t>RP 505 valve stations (stem packing, flanges), 3 m</t>
+        </is>
+      </c>
+      <c r="S148" s="5" t="inlineStr">
+        <is>
+          <t>Indicative location (P&amp;ID / piping layout not yet issued)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n">
+        <v>145</v>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>RS-147</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>Control-valve station</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>Control valves FV-2022 (P-203)</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>P-203</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>Slop wax</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr"/>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>Open, adequate (natural)</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>Zone 2</t>
+        </is>
+      </c>
+      <c r="M149" s="4" t="inlineStr">
+        <is>
+          <t>Z2: R 3</t>
+        </is>
+      </c>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>100.0-104.0</t>
+        </is>
+      </c>
+      <c r="O149" s="4" t="inlineStr">
+        <is>
+          <t>IIA</t>
+        </is>
+      </c>
+      <c r="P149" s="4" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="Q149" s="4" t="inlineStr">
+        <is>
+          <t>180.0 / 88.0</t>
+        </is>
+      </c>
+      <c r="R149" s="5" t="inlineStr">
+        <is>
+          <t>RP 505 valve stations (stem packing, flanges), 3 m</t>
+        </is>
+      </c>
+      <c r="S149" s="5" t="inlineStr">
+        <is>
+          <t>Indicative location (P&amp;ID / piping layout not yet issued)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>RS-148</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>Control-valve station</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>Control valves FV-2025 (P-204)</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>P-204</t>
+        </is>
+      </c>
+      <c r="F150" s="5" t="inlineStr">
+        <is>
+          <t>Vacuum residue &gt; AIT</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr"/>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>Secondary</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>Open, adequate (natural)</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>Zone 2</t>
+        </is>
+      </c>
+      <c r="M150" s="4" t="inlineStr">
+        <is>
+          <t>Z2: R 3</t>
+        </is>
+      </c>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>100.0-104.0</t>
+        </is>
+      </c>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>IIA</t>
+        </is>
+      </c>
+      <c r="P150" s="4" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="Q150" s="4" t="inlineStr">
+        <is>
           <t>173.5 / 88.0</t>
         </is>
       </c>
-      <c r="R148" s="5" t="inlineStr">
+      <c r="R150" s="5" t="inlineStr">
         <is>
           <t>RP 505 valve stations (stem packing, flanges), 3 m</t>
         </is>
       </c>
-      <c r="S148" s="5" t="inlineStr">
+      <c r="S150" s="5" t="inlineStr">
         <is>
           <t>Indicative location (P&amp;ID / piping layout not yet issued)</t>
         </is>
@@ -13430,11 +13604,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.6</v>
+        <v>10.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RS-130</t>
+          <t>RS-132</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13455,11 +13629,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RS-124</t>
+          <t>RS-126</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13484,7 +13658,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>RS-130</t>
+          <t>RS-132</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/deliverables/05-electrical/CFU-000-EL-HAC-003_Release-Source-Schedule.xlsx
+++ b/deliverables/05-electrical/CFU-000-EL-HAC-003_Release-Source-Schedule.xlsx
@@ -9621,7 +9621,7 @@
       </c>
       <c r="Q107" s="4" t="inlineStr">
         <is>
-          <t>51.0 / 75.0</t>
+          <t>45.0 / 75.0</t>
         </is>
       </c>
       <c r="R107" s="5" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="Q108" s="4" t="inlineStr">
         <is>
-          <t>57.0 / 75.0</t>
+          <t>51.0 / 75.0</t>
         </is>
       </c>
       <c r="R108" s="5" t="inlineStr">
